--- a/data/matches/leagues/Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/matches/leagues/Turkey_Süper_Lig_2025-2026.xlsx
@@ -54497,10 +54497,10 @@
         <v>7</v>
       </c>
       <c r="Y113" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Z113" t="n">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="AA113" t="inlineStr"/>
       <c r="AB113" t="inlineStr"/>
@@ -55433,10 +55433,10 @@
         <v>17</v>
       </c>
       <c r="Y115" t="n">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="Z115" t="n">
-        <v>38</v>
+        <v>39</v>
       </c>
       <c r="AA115" t="inlineStr"/>
       <c r="AB115" t="inlineStr"/>

--- a/data/matches/leagues/Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/matches/leagues/Turkey_Süper_Lig_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP118" headerRowCount="1">
-  <autoFilter ref="A1:EP118"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EP119" headerRowCount="1">
+  <autoFilter ref="A1:EP119"/>
   <tableColumns count="146">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -584,7 +584,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EP118"/>
+  <dimension ref="A1:EP119"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -2277,7 +2277,7 @@
         <v>1.71</v>
       </c>
       <c r="DE3" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF3" t="n">
         <v>0</v>
@@ -5138,7 +5138,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE9" t="n">
         <v>2</v>
@@ -9453,7 +9453,7 @@
         <v>1.57</v>
       </c>
       <c r="DE18" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF18" t="n">
         <v>0</v>
@@ -12346,7 +12346,7 @@
         <v>50</v>
       </c>
       <c r="DD24" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE24" t="n">
         <v>0.67</v>
@@ -19981,7 +19981,7 @@
         <v>1</v>
       </c>
       <c r="DE40" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF40" t="n">
         <v>0</v>
@@ -24262,7 +24262,7 @@
         <v>25</v>
       </c>
       <c r="DD49" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE49" t="n">
         <v>1.17</v>
@@ -30005,7 +30005,7 @@
         <v>0.71</v>
       </c>
       <c r="DE61" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF61" t="n">
         <v>0.33</v>
@@ -32382,7 +32382,7 @@
         <v>50</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE66" t="n">
         <v>0.17</v>
@@ -36145,7 +36145,7 @@
         <v>1.67</v>
       </c>
       <c r="DE74" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF74" t="n">
         <v>3</v>
@@ -40902,7 +40902,7 @@
         <v>63</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE84" t="n">
         <v>1</v>
@@ -45225,7 +45225,7 @@
         <v>2</v>
       </c>
       <c r="DE93" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF93" t="n">
         <v>2</v>
@@ -50199,40 +50199,40 @@
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>Antalyaspor</t>
+          <t>Kasımpaşa</t>
         </is>
       </c>
       <c r="E104" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="F104" s="2" t="n">
         <v>45969.70833333334</v>
       </c>
       <c r="G104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I104" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="J104" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="K104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="L104" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="M104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="N104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="O104" t="n">
         <v>0</v>
@@ -50241,122 +50241,122 @@
         <v>0</v>
       </c>
       <c r="Q104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="R104" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="S104" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="T104" t="n">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="U104" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="V104" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="W104" t="n">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="X104" t="n">
-        <v>18</v>
+        <v>24</v>
       </c>
       <c r="Y104" t="n">
-        <v>46</v>
+        <v>68</v>
       </c>
       <c r="Z104" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>Antalya Stadyumu</t>
+          <t>Recep Tayyip Erdoğan Stadyumu</t>
         </is>
       </c>
       <c r="AB104" t="inlineStr">
         <is>
-          <t>100. Yıl Bulvarı, Antalya</t>
+          <t>Tepebaşı Caddesi, Kasımpaşa, Beyoğlu, İstanbul</t>
         </is>
       </c>
       <c r="AC104" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AD104" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE104" t="n">
-        <v>4.71</v>
+        <v>3.45</v>
       </c>
       <c r="AF104" t="n">
-        <v>4.18</v>
+        <v>3.35</v>
       </c>
       <c r="AG104" t="n">
-        <v>1.67</v>
+        <v>2.15</v>
       </c>
       <c r="AH104" t="n">
-        <v>1.15</v>
+        <v>1.36</v>
       </c>
       <c r="AI104" t="n">
-        <v>1.66</v>
+        <v>2.16</v>
       </c>
       <c r="AJ104" t="n">
-        <v>2.68</v>
+        <v>3.87</v>
       </c>
       <c r="AK104" t="n">
-        <v>1.69</v>
+        <v>1.83</v>
       </c>
       <c r="AL104" t="n">
-        <v>2.13</v>
+        <v>1.91</v>
       </c>
       <c r="AM104" t="n">
-        <v>1.49</v>
+        <v>1.52</v>
       </c>
       <c r="AN104" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="AO104" t="n">
-        <v>2.44</v>
+        <v>2.27</v>
       </c>
       <c r="AP104" t="n">
-        <v>1.97</v>
+        <v>1.78</v>
       </c>
       <c r="AQ104" t="n">
-        <v>1.3</v>
+        <v>1.44</v>
       </c>
       <c r="AR104" t="n">
-        <v>2.4</v>
+        <v>3.02</v>
       </c>
       <c r="AS104" t="n">
-        <v>3.3</v>
+        <v>2.65</v>
       </c>
       <c r="AT104" t="n">
-        <v>1.49</v>
+        <v>1.33</v>
       </c>
       <c r="AU104" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="AV104" t="n">
         <v>0</v>
       </c>
       <c r="AW104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AX104" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AY104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AZ104" t="n">
         <v>2</v>
       </c>
       <c r="BA104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BB104" t="n">
-        <v>109</v>
+        <v>357</v>
       </c>
       <c r="BC104" t="n">
         <v>0</v>
@@ -50377,178 +50377,178 @@
         <v>1</v>
       </c>
       <c r="BI104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BJ104" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BK104" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BL104" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BM104" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BN104" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="BO104" t="n">
         <v>1</v>
       </c>
       <c r="BP104" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BQ104" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BR104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS104" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BT104" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU104" t="n">
         <v>1</v>
       </c>
       <c r="BV104" t="n">
+        <v>63</v>
+      </c>
+      <c r="BW104" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX104" t="n">
+        <v>99</v>
+      </c>
+      <c r="BY104" t="n">
+        <v>74</v>
+      </c>
+      <c r="BZ104" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="CA104" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="CB104" t="n">
+        <v>2.89</v>
+      </c>
+      <c r="CC104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP104" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR104" t="n">
+        <v>30</v>
+      </c>
+      <c r="CS104" t="n">
+        <v>12</v>
+      </c>
+      <c r="CT104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU104" t="n">
+        <v>24</v>
+      </c>
+      <c r="CV104" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW104" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX104" t="n">
+        <v>12</v>
+      </c>
+      <c r="CY104" t="n">
+        <v>9</v>
+      </c>
+      <c r="CZ104" t="n">
+        <v>27</v>
+      </c>
+      <c r="DA104" t="n">
+        <v>74</v>
+      </c>
+      <c r="DB104" t="n">
         <v>29</v>
       </c>
-      <c r="BW104" t="n">
-        <v>31</v>
-      </c>
-      <c r="BX104" t="n">
-        <v>85</v>
-      </c>
-      <c r="BY104" t="n">
-        <v>111</v>
-      </c>
-      <c r="BZ104" t="n">
-        <v>0.61</v>
-      </c>
-      <c r="CA104" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="CB104" t="n">
-        <v>2.01</v>
-      </c>
-      <c r="CC104" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD104" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE104" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF104" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG104" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH104" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI104" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ104" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK104" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL104" t="n">
-        <v>1</v>
-      </c>
-      <c r="CM104" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN104" t="n">
-        <v>1</v>
-      </c>
-      <c r="CO104" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP104" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ104" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR104" t="n">
-        <v>17</v>
-      </c>
-      <c r="CS104" t="n">
-        <v>21</v>
-      </c>
-      <c r="CT104" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU104" t="n">
-        <v>18</v>
-      </c>
-      <c r="CV104" t="n">
-        <v>13</v>
-      </c>
-      <c r="CW104" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX104" t="n">
-        <v>5</v>
-      </c>
-      <c r="CY104" t="n">
-        <v>3</v>
-      </c>
-      <c r="CZ104" t="n">
+      <c r="DC104" t="n">
         <v>57</v>
       </c>
-      <c r="DA104" t="n">
-        <v>100</v>
-      </c>
-      <c r="DB104" t="n">
-        <v>65</v>
-      </c>
-      <c r="DC104" t="n">
-        <v>90</v>
-      </c>
       <c r="DD104" t="n">
-        <v>0.67</v>
+        <v>0.5</v>
       </c>
       <c r="DE104" t="n">
         <v>1.57</v>
       </c>
       <c r="DF104" t="n">
-        <v>0.8</v>
+        <v>0.6</v>
       </c>
       <c r="DG104" t="n">
         <v>1.33</v>
       </c>
       <c r="DH104" t="n">
-        <v>1.18</v>
+        <v>0.91</v>
       </c>
       <c r="DI104" t="n">
-        <v>1.55</v>
+        <v>1.73</v>
       </c>
       <c r="DJ104" t="n">
-        <v>44</v>
+        <v>74</v>
       </c>
       <c r="DK104" t="n">
-        <v>0</v>
+        <v>27</v>
       </c>
       <c r="DL104" t="n">
-        <v>1.42</v>
+        <v>1.36</v>
       </c>
       <c r="DM104" t="n">
-        <v>1.48</v>
+        <v>1.45</v>
       </c>
       <c r="DN104" t="n">
-        <v>2.9</v>
+        <v>2.81</v>
       </c>
       <c r="DO104" t="n">
         <v>13</v>
@@ -50560,10 +50560,10 @@
         <v>1</v>
       </c>
       <c r="DR104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT104" t="b">
         <v>0</v>
@@ -50572,70 +50572,86 @@
         <v>0</v>
       </c>
       <c r="DV104" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW104" t="n">
-        <v>22.86</v>
+        <v>17.52</v>
       </c>
       <c r="DX104" t="n">
-        <v>2.71</v>
+        <v>1.52</v>
       </c>
       <c r="DY104" t="inlineStr">
         <is>
-          <t>48%</t>
+          <t>69%</t>
         </is>
       </c>
       <c r="DZ104" t="inlineStr">
         <is>
-          <t>5%</t>
+          <t>100%</t>
         </is>
       </c>
       <c r="EA104" t="inlineStr">
         <is>
-          <t>1.68</t>
+          <t>2.17</t>
         </is>
       </c>
       <c r="EB104" t="inlineStr">
         <is>
-          <t>2.66</t>
+          <t>3.86</t>
         </is>
       </c>
       <c r="EC104" t="inlineStr">
         <is>
-          <t>1.21</t>
+          <t>1.36</t>
         </is>
       </c>
       <c r="ED104" t="inlineStr"/>
       <c r="EE104" t="inlineStr"/>
       <c r="EF104" t="inlineStr"/>
       <c r="EG104" t="inlineStr"/>
-      <c r="EH104" t="inlineStr"/>
-      <c r="EI104" t="inlineStr"/>
-      <c r="EJ104" t="inlineStr"/>
-      <c r="EK104" t="inlineStr"/>
+      <c r="EH104" t="inlineStr">
+        <is>
+          <t>1.55</t>
+        </is>
+      </c>
+      <c r="EI104" t="inlineStr">
+        <is>
+          <t>1.84</t>
+        </is>
+      </c>
+      <c r="EJ104" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="EK104" t="inlineStr">
+        <is>
+          <t>1.97</t>
+        </is>
+      </c>
       <c r="EL104" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>2.19</t>
         </is>
       </c>
       <c r="EM104" t="inlineStr">
         <is>
-          <t>4.89</t>
+          <t>3.61</t>
         </is>
       </c>
       <c r="EN104" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>3.32</t>
         </is>
       </c>
       <c r="EO104" t="inlineStr">
         <is>
-          <t>1.69</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="EP104" t="inlineStr">
         <is>
-          <t>2.24</t>
+          <t>2.00</t>
         </is>
       </c>
     </row>
@@ -50655,164 +50671,164 @@
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>Kasımpaşa</t>
+          <t>Antalyaspor</t>
         </is>
       </c>
       <c r="E105" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F105" s="2" t="n">
         <v>45969.70833333334</v>
       </c>
       <c r="G105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H105" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="J105" t="n">
+        <v>3</v>
+      </c>
+      <c r="K105" t="n">
+        <v>3</v>
+      </c>
+      <c r="L105" t="n">
+        <v>6</v>
+      </c>
+      <c r="M105" t="n">
+        <v>3</v>
+      </c>
+      <c r="N105" t="n">
+        <v>1</v>
+      </c>
+      <c r="O105" t="n">
+        <v>0</v>
+      </c>
+      <c r="P105" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q105" t="n">
+        <v>1</v>
+      </c>
+      <c r="R105" t="n">
         <v>5</v>
       </c>
-      <c r="K105" t="n">
-        <v>2</v>
-      </c>
-      <c r="L105" t="n">
-        <v>7</v>
-      </c>
-      <c r="M105" t="n">
-        <v>1</v>
-      </c>
-      <c r="N105" t="n">
-        <v>3</v>
-      </c>
-      <c r="O105" t="n">
-        <v>0</v>
-      </c>
-      <c r="P105" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q105" t="n">
-        <v>3</v>
-      </c>
-      <c r="R105" t="n">
-        <v>3</v>
-      </c>
       <c r="S105" t="n">
-        <v>9</v>
+        <v>4</v>
       </c>
       <c r="T105" t="n">
-        <v>12</v>
+        <v>8</v>
       </c>
       <c r="U105" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="V105" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="W105" t="n">
-        <v>7</v>
+        <v>13</v>
       </c>
       <c r="X105" t="n">
-        <v>24</v>
+        <v>18</v>
       </c>
       <c r="Y105" t="n">
-        <v>68</v>
+        <v>46</v>
       </c>
       <c r="Z105" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>Recep Tayyip Erdoğan Stadyumu</t>
+          <t>Antalya Stadyumu</t>
         </is>
       </c>
       <c r="AB105" t="inlineStr">
         <is>
-          <t>Tepebaşı Caddesi, Kasımpaşa, Beyoğlu, İstanbul</t>
+          <t>100. Yıl Bulvarı, Antalya</t>
         </is>
       </c>
       <c r="AC105" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AD105" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE105" t="n">
-        <v>3.45</v>
+        <v>4.71</v>
       </c>
       <c r="AF105" t="n">
-        <v>3.35</v>
+        <v>4.18</v>
       </c>
       <c r="AG105" t="n">
-        <v>2.15</v>
+        <v>1.67</v>
       </c>
       <c r="AH105" t="n">
-        <v>1.36</v>
+        <v>1.15</v>
       </c>
       <c r="AI105" t="n">
-        <v>2.16</v>
+        <v>1.66</v>
       </c>
       <c r="AJ105" t="n">
-        <v>3.87</v>
+        <v>2.68</v>
       </c>
       <c r="AK105" t="n">
+        <v>1.69</v>
+      </c>
+      <c r="AL105" t="n">
+        <v>2.13</v>
+      </c>
+      <c r="AM105" t="n">
+        <v>1.49</v>
+      </c>
+      <c r="AN105" t="n">
         <v>1.83</v>
       </c>
-      <c r="AL105" t="n">
-        <v>1.91</v>
-      </c>
-      <c r="AM105" t="n">
-        <v>1.52</v>
-      </c>
-      <c r="AN105" t="n">
-        <v>2</v>
-      </c>
       <c r="AO105" t="n">
-        <v>2.27</v>
+        <v>2.44</v>
       </c>
       <c r="AP105" t="n">
-        <v>1.78</v>
+        <v>1.97</v>
       </c>
       <c r="AQ105" t="n">
-        <v>1.44</v>
+        <v>1.3</v>
       </c>
       <c r="AR105" t="n">
-        <v>3.02</v>
+        <v>2.4</v>
       </c>
       <c r="AS105" t="n">
-        <v>2.65</v>
+        <v>3.3</v>
       </c>
       <c r="AT105" t="n">
-        <v>1.33</v>
+        <v>1.49</v>
       </c>
       <c r="AU105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="AV105" t="n">
         <v>0</v>
       </c>
       <c r="AW105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AX105" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AY105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AZ105" t="n">
         <v>2</v>
       </c>
       <c r="BA105" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BB105" t="n">
-        <v>357</v>
+        <v>109</v>
       </c>
       <c r="BC105" t="n">
         <v>0</v>
@@ -50833,178 +50849,178 @@
         <v>1</v>
       </c>
       <c r="BI105" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BJ105" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="BK105" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BL105" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BM105" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BN105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP105" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ105" t="n">
+        <v>2</v>
+      </c>
+      <c r="BR105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BS105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BT105" t="n">
+        <v>3</v>
+      </c>
+      <c r="BU105" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV105" t="n">
+        <v>29</v>
+      </c>
+      <c r="BW105" t="n">
+        <v>31</v>
+      </c>
+      <c r="BX105" t="n">
+        <v>85</v>
+      </c>
+      <c r="BY105" t="n">
+        <v>111</v>
+      </c>
+      <c r="BZ105" t="n">
+        <v>0.61</v>
+      </c>
+      <c r="CA105" t="n">
+        <v>1.41</v>
+      </c>
+      <c r="CB105" t="n">
+        <v>2.01</v>
+      </c>
+      <c r="CC105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CM105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CO105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP105" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR105" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS105" t="n">
+        <v>21</v>
+      </c>
+      <c r="CT105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU105" t="n">
+        <v>18</v>
+      </c>
+      <c r="CV105" t="n">
+        <v>13</v>
+      </c>
+      <c r="CW105" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX105" t="n">
         <v>5</v>
       </c>
-      <c r="BO105" t="n">
-        <v>1</v>
-      </c>
-      <c r="BP105" t="n">
-        <v>1</v>
-      </c>
-      <c r="BQ105" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR105" t="n">
-        <v>2</v>
-      </c>
-      <c r="BS105" t="n">
-        <v>2</v>
-      </c>
-      <c r="BT105" t="n">
-        <v>2</v>
-      </c>
-      <c r="BU105" t="n">
-        <v>1</v>
-      </c>
-      <c r="BV105" t="n">
-        <v>63</v>
-      </c>
-      <c r="BW105" t="n">
-        <v>44</v>
-      </c>
-      <c r="BX105" t="n">
-        <v>99</v>
-      </c>
-      <c r="BY105" t="n">
-        <v>74</v>
-      </c>
-      <c r="BZ105" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="CA105" t="n">
-        <v>1.47</v>
-      </c>
-      <c r="CB105" t="n">
-        <v>2.89</v>
-      </c>
-      <c r="CC105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CN105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP105" t="n">
-        <v>0</v>
-      </c>
-      <c r="CQ105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR105" t="n">
-        <v>30</v>
-      </c>
-      <c r="CS105" t="n">
-        <v>12</v>
-      </c>
-      <c r="CT105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU105" t="n">
-        <v>24</v>
-      </c>
-      <c r="CV105" t="n">
-        <v>7</v>
-      </c>
-      <c r="CW105" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX105" t="n">
-        <v>12</v>
-      </c>
       <c r="CY105" t="n">
-        <v>9</v>
+        <v>3</v>
       </c>
       <c r="CZ105" t="n">
-        <v>27</v>
+        <v>57</v>
       </c>
       <c r="DA105" t="n">
-        <v>74</v>
+        <v>100</v>
       </c>
       <c r="DB105" t="n">
-        <v>29</v>
+        <v>65</v>
       </c>
       <c r="DC105" t="n">
-        <v>57</v>
+        <v>90</v>
       </c>
       <c r="DD105" t="n">
-        <v>0.5</v>
+        <v>0.67</v>
       </c>
       <c r="DE105" t="n">
         <v>1.57</v>
       </c>
       <c r="DF105" t="n">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="DG105" t="n">
         <v>1.33</v>
       </c>
       <c r="DH105" t="n">
-        <v>0.91</v>
+        <v>1.18</v>
       </c>
       <c r="DI105" t="n">
-        <v>1.73</v>
+        <v>1.55</v>
       </c>
       <c r="DJ105" t="n">
-        <v>74</v>
+        <v>44</v>
       </c>
       <c r="DK105" t="n">
-        <v>27</v>
+        <v>0</v>
       </c>
       <c r="DL105" t="n">
-        <v>1.36</v>
+        <v>1.42</v>
       </c>
       <c r="DM105" t="n">
-        <v>1.45</v>
+        <v>1.48</v>
       </c>
       <c r="DN105" t="n">
-        <v>2.81</v>
+        <v>2.9</v>
       </c>
       <c r="DO105" t="n">
         <v>13</v>
@@ -51016,10 +51032,10 @@
         <v>1</v>
       </c>
       <c r="DR105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT105" t="b">
         <v>0</v>
@@ -51028,86 +51044,70 @@
         <v>0</v>
       </c>
       <c r="DV105" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW105" t="n">
-        <v>17.52</v>
+        <v>22.86</v>
       </c>
       <c r="DX105" t="n">
-        <v>1.52</v>
+        <v>2.71</v>
       </c>
       <c r="DY105" t="inlineStr">
         <is>
-          <t>69%</t>
+          <t>48%</t>
         </is>
       </c>
       <c r="DZ105" t="inlineStr">
         <is>
-          <t>100%</t>
+          <t>5%</t>
         </is>
       </c>
       <c r="EA105" t="inlineStr">
         <is>
-          <t>2.17</t>
+          <t>1.68</t>
         </is>
       </c>
       <c r="EB105" t="inlineStr">
         <is>
-          <t>3.86</t>
+          <t>2.66</t>
         </is>
       </c>
       <c r="EC105" t="inlineStr">
         <is>
-          <t>1.36</t>
+          <t>1.21</t>
         </is>
       </c>
       <c r="ED105" t="inlineStr"/>
       <c r="EE105" t="inlineStr"/>
       <c r="EF105" t="inlineStr"/>
       <c r="EG105" t="inlineStr"/>
-      <c r="EH105" t="inlineStr">
-        <is>
-          <t>1.55</t>
-        </is>
-      </c>
-      <c r="EI105" t="inlineStr">
-        <is>
-          <t>1.84</t>
-        </is>
-      </c>
-      <c r="EJ105" t="inlineStr">
-        <is>
-          <t>2.35</t>
-        </is>
-      </c>
-      <c r="EK105" t="inlineStr">
-        <is>
-          <t>1.97</t>
-        </is>
-      </c>
+      <c r="EH105" t="inlineStr"/>
+      <c r="EI105" t="inlineStr"/>
+      <c r="EJ105" t="inlineStr"/>
+      <c r="EK105" t="inlineStr"/>
       <c r="EL105" t="inlineStr">
         <is>
-          <t>2.19</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EM105" t="inlineStr">
         <is>
-          <t>3.61</t>
+          <t>4.89</t>
         </is>
       </c>
       <c r="EN105" t="inlineStr">
         <is>
-          <t>3.32</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="EO105" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>1.69</t>
         </is>
       </c>
       <c r="EP105" t="inlineStr">
         <is>
-          <t>2.00</t>
+          <t>2.24</t>
         </is>
       </c>
     </row>
@@ -51934,7 +51934,7 @@
         <v>50</v>
       </c>
       <c r="DD107" t="n">
-        <v>1.83</v>
+        <v>2</v>
       </c>
       <c r="DE107" t="n">
         <v>2.5</v>
@@ -54273,7 +54273,7 @@
         <v>2.43</v>
       </c>
       <c r="DE112" t="n">
-        <v>0.57</v>
+        <v>0.5</v>
       </c>
       <c r="DF112" t="n">
         <v>2.33</v>
@@ -57284,6 +57284,494 @@
       <c r="EP118" t="inlineStr">
         <is>
           <t>2.09</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>Turkey_Süper_Lig_2025-2026</t>
+        </is>
+      </c>
+      <c r="B119" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C119" t="n">
+        <v>14</v>
+      </c>
+      <c r="D119" t="inlineStr">
+        <is>
+          <t>Kocaelispor</t>
+        </is>
+      </c>
+      <c r="E119" t="inlineStr">
+        <is>
+          <t>Gençlerbirliği</t>
+        </is>
+      </c>
+      <c r="F119" s="2" t="n">
+        <v>45989.70833333334</v>
+      </c>
+      <c r="G119" t="n">
+        <v>1</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0</v>
+      </c>
+      <c r="I119" t="n">
+        <v>1</v>
+      </c>
+      <c r="J119" t="n">
+        <v>6</v>
+      </c>
+      <c r="K119" t="n">
+        <v>1</v>
+      </c>
+      <c r="L119" t="n">
+        <v>7</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>4</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0</v>
+      </c>
+      <c r="S119" t="n">
+        <v>11</v>
+      </c>
+      <c r="T119" t="n">
+        <v>5</v>
+      </c>
+      <c r="U119" t="n">
+        <v>15</v>
+      </c>
+      <c r="V119" t="n">
+        <v>5</v>
+      </c>
+      <c r="W119" t="n">
+        <v>16</v>
+      </c>
+      <c r="X119" t="n">
+        <v>15</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>53</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>47</v>
+      </c>
+      <c r="AA119" t="inlineStr">
+        <is>
+          <t>İsmetpaşa Stadyumu</t>
+        </is>
+      </c>
+      <c r="AB119" t="inlineStr">
+        <is>
+          <t>Ankara Caddesi, Kocaeli, İzmit</t>
+        </is>
+      </c>
+      <c r="AC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>1.97</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>4.25</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>2.12</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>3.7</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>1.87</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>2.05</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>3</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>2.75</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>1</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>11088</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>52</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>4</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>2</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>52</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>118</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>82</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>1.61</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>2.11</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>17</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU119" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV119" t="n">
+        <v>16</v>
+      </c>
+      <c r="CW119" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX119" t="n">
+        <v>7</v>
+      </c>
+      <c r="CY119" t="n">
+        <v>7</v>
+      </c>
+      <c r="CZ119" t="n">
+        <v>29</v>
+      </c>
+      <c r="DA119" t="n">
+        <v>61</v>
+      </c>
+      <c r="DB119" t="n">
+        <v>16</v>
+      </c>
+      <c r="DC119" t="n">
+        <v>52</v>
+      </c>
+      <c r="DD119" t="n">
+        <v>2</v>
+      </c>
+      <c r="DE119" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="DF119" t="n">
+        <v>1.83</v>
+      </c>
+      <c r="DG119" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="DH119" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="DI119" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="DJ119" t="n">
+        <v>72</v>
+      </c>
+      <c r="DK119" t="n">
+        <v>40</v>
+      </c>
+      <c r="DL119" t="n">
+        <v>1.28</v>
+      </c>
+      <c r="DM119" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="DN119" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="DO119" t="n">
+        <v>14</v>
+      </c>
+      <c r="DP119" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DR119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV119" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW119" t="n">
+        <v>19.48</v>
+      </c>
+      <c r="DX119" t="n">
+        <v>2.63</v>
+      </c>
+      <c r="DY119" t="inlineStr">
+        <is>
+          <t>48%</t>
+        </is>
+      </c>
+      <c r="DZ119" t="inlineStr">
+        <is>
+          <t>32%</t>
+        </is>
+      </c>
+      <c r="EA119" t="inlineStr">
+        <is>
+          <t>2.08</t>
+        </is>
+      </c>
+      <c r="EB119" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="EC119" t="inlineStr">
+        <is>
+          <t>1.34</t>
+        </is>
+      </c>
+      <c r="ED119" t="inlineStr">
+        <is>
+          <t>3.19</t>
+        </is>
+      </c>
+      <c r="EE119" t="inlineStr">
+        <is>
+          <t>1.37</t>
+        </is>
+      </c>
+      <c r="EF119" t="inlineStr">
+        <is>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="EG119" t="inlineStr">
+        <is>
+          <t>2.84</t>
+        </is>
+      </c>
+      <c r="EH119" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EI119" t="inlineStr">
+        <is>
+          <t>1.67</t>
+        </is>
+      </c>
+      <c r="EJ119" t="inlineStr">
+        <is>
+          <t>2.10</t>
+        </is>
+      </c>
+      <c r="EK119" t="inlineStr">
+        <is>
+          <t>2.17</t>
+        </is>
+      </c>
+      <c r="EL119" t="inlineStr">
+        <is>
+          <t>5.62</t>
+        </is>
+      </c>
+      <c r="EM119" t="inlineStr">
+        <is>
+          <t>1.71</t>
+        </is>
+      </c>
+      <c r="EN119" t="inlineStr">
+        <is>
+          <t>3.63</t>
+        </is>
+      </c>
+      <c r="EO119" t="inlineStr">
+        <is>
+          <t>1.96</t>
+        </is>
+      </c>
+      <c r="EP119" t="inlineStr">
+        <is>
+          <t>1.89</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/matches/leagues/Turkey_Süper_Lig_2025-2026.xlsx
@@ -72653,10 +72653,10 @@
         <v>13</v>
       </c>
       <c r="Y151" t="n">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="Z151" t="n">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="AA151" t="inlineStr"/>
       <c r="AB151" t="inlineStr"/>

--- a/data/matches/leagues/Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/matches/leagues/Turkey_Süper_Lig_2025-2026.xlsx
@@ -36947,28 +36947,28 @@
         <v>-1</v>
       </c>
       <c r="BG76" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BH76" t="n">
         <v>1</v>
       </c>
       <c r="BI76" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BJ76" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="BK76" t="n">
-        <v>2</v>
+        <v>-1</v>
       </c>
       <c r="BL76" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BM76" t="n">
-        <v>5</v>
+        <v>-1</v>
       </c>
       <c r="BN76" t="n">
-        <v>7</v>
+        <v>-1</v>
       </c>
       <c r="BO76" t="n">
         <v>2</v>
@@ -37043,10 +37043,10 @@
         <v>0</v>
       </c>
       <c r="CM76" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="CN76" t="n">
-        <v>0</v>
+        <v>-1</v>
       </c>
       <c r="CO76" t="n">
         <v>0</v>
@@ -37293,10 +37293,10 @@
         <v>11</v>
       </c>
       <c r="M77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="N77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="O77" t="n">
         <v>0</v>
@@ -37345,10 +37345,10 @@
         </is>
       </c>
       <c r="AC77" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="AD77" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AE77" t="n">
         <v>1.83</v>
@@ -37465,16 +37465,16 @@
         <v>4</v>
       </c>
       <c r="BQ77" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="BR77" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BS77" t="n">
         <v>5</v>
       </c>
       <c r="BT77" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="BU77" t="n">
         <v>1</v>
@@ -62628,7 +62628,7 @@
         <v>0</v>
       </c>
       <c r="N130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="O130" t="n">
         <v>0</v>
@@ -62680,7 +62680,7 @@
         <v>0</v>
       </c>
       <c r="AD130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE130" t="n">
         <v>2.3</v>
@@ -62800,13 +62800,13 @@
         <v>0</v>
       </c>
       <c r="BR130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BS130" t="n">
         <v>0</v>
       </c>
       <c r="BT130" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU130" t="n">
         <v>1</v>
@@ -69331,13 +69331,13 @@
         <v>6</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="T144" t="n">
         <v>6</v>
       </c>
       <c r="U144" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="V144" t="n">
         <v>12</v>
@@ -69512,13 +69512,13 @@
         <v>113</v>
       </c>
       <c r="BZ144" t="n">
-        <v>1.52</v>
+        <v>1.58</v>
       </c>
       <c r="CA144" t="n">
         <v>1.51</v>
       </c>
       <c r="CB144" t="n">
-        <v>3.03</v>
+        <v>3.09</v>
       </c>
       <c r="CC144" t="n">
         <v>0</v>

--- a/data/matches/leagues/Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/matches/leagues/Turkey_Süper_Lig_2025-2026.xlsx
@@ -141,8 +141,8 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL180" headerRowCount="1">
-  <autoFilter ref="A1:EL180"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" id="1" name="MatchesTable" displayName="MatchesTable" ref="A1:EL181" headerRowCount="1">
+  <autoFilter ref="A1:EL181"/>
   <tableColumns count="142">
     <tableColumn id="1" name="league"/>
     <tableColumn id="2" name="season"/>
@@ -580,7 +580,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:EL180"/>
+  <dimension ref="A1:EL181"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33.6" customWidth="1" min="1" max="1"/>
@@ -4111,7 +4111,7 @@
         <v>0</v>
       </c>
       <c r="DO7" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP7" t="b">
         <v>1</v>
@@ -4998,7 +4998,7 @@
         <v>0</v>
       </c>
       <c r="DD9" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE9" t="n">
         <v>1.6</v>
@@ -5031,7 +5031,7 @@
         <v>0</v>
       </c>
       <c r="DO9" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP9" t="b">
         <v>1</v>
@@ -5905,7 +5905,7 @@
         <v>2.1</v>
       </c>
       <c r="DE11" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DF11" t="n">
         <v>0</v>
@@ -5935,7 +5935,7 @@
         <v>0</v>
       </c>
       <c r="DO11" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP11" t="b">
         <v>0</v>
@@ -9671,7 +9671,7 @@
         <v>1.22</v>
       </c>
       <c r="DO19" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP19" t="b">
         <v>1</v>
@@ -12414,7 +12414,7 @@
         <v>50</v>
       </c>
       <c r="DD25" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE25" t="n">
         <v>0.82</v>
@@ -12447,7 +12447,7 @@
         <v>2.48</v>
       </c>
       <c r="DO25" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP25" t="b">
         <v>1</v>
@@ -14257,7 +14257,7 @@
         <v>1.7</v>
       </c>
       <c r="DE29" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DF29" t="n">
         <v>0</v>
@@ -14287,7 +14287,7 @@
         <v>2.4</v>
       </c>
       <c r="DO29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP29" t="b">
         <v>1</v>
@@ -18455,7 +18455,7 @@
         <v>3.1</v>
       </c>
       <c r="DO38" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP38" t="b">
         <v>1</v>
@@ -18919,7 +18919,7 @@
         <v>2.36</v>
       </c>
       <c r="DO39" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP39" t="b">
         <v>1</v>
@@ -20775,7 +20775,7 @@
         <v>3.77</v>
       </c>
       <c r="DO43" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP43" t="b">
         <v>1</v>
@@ -23482,7 +23482,7 @@
         <v>25</v>
       </c>
       <c r="DD49" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE49" t="n">
         <v>0.9</v>
@@ -23515,7 +23515,7 @@
         <v>2.21</v>
       </c>
       <c r="DO49" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP49" t="b">
         <v>1</v>
@@ -23957,7 +23957,7 @@
         <v>0.5</v>
       </c>
       <c r="DE50" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DF50" t="n">
         <v>0</v>
@@ -23987,7 +23987,7 @@
         <v>2.74</v>
       </c>
       <c r="DO50" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP50" t="b">
         <v>1</v>
@@ -28619,7 +28619,7 @@
         <v>3.41</v>
       </c>
       <c r="DO60" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP60" t="b">
         <v>1</v>
@@ -29527,7 +29527,7 @@
         <v>2.98</v>
       </c>
       <c r="DO62" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP62" t="b">
         <v>1</v>
@@ -31330,7 +31330,7 @@
         <v>50</v>
       </c>
       <c r="DD66" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE66" t="n">
         <v>0.8</v>
@@ -31363,7 +31363,7 @@
         <v>2.85</v>
       </c>
       <c r="DO66" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP66" t="b">
         <v>1</v>
@@ -33621,7 +33621,7 @@
         <v>1.4</v>
       </c>
       <c r="DE71" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DF71" t="n">
         <v>1.75</v>
@@ -33651,7 +33651,7 @@
         <v>2.52</v>
       </c>
       <c r="DO71" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP71" t="b">
         <v>0</v>
@@ -34107,7 +34107,7 @@
         <v>2.4</v>
       </c>
       <c r="DO72" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP72" t="b">
         <v>1</v>
@@ -37299,7 +37299,7 @@
         <v>3.72</v>
       </c>
       <c r="DO79" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP79" t="b">
         <v>1</v>
@@ -39562,7 +39562,7 @@
         <v>63</v>
       </c>
       <c r="DD84" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE84" t="n">
         <v>1</v>
@@ -39595,7 +39595,7 @@
         <v>2.48</v>
       </c>
       <c r="DO84" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP84" t="b">
         <v>1</v>
@@ -42805,7 +42805,7 @@
         <v>1.2</v>
       </c>
       <c r="DE91" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DF91" t="n">
         <v>2</v>
@@ -42835,7 +42835,7 @@
         <v>2.94</v>
       </c>
       <c r="DO91" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP91" t="b">
         <v>1</v>
@@ -43307,7 +43307,7 @@
         <v>2.02</v>
       </c>
       <c r="DO92" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP92" t="b">
         <v>1</v>
@@ -45589,7 +45589,7 @@
         <v>2</v>
       </c>
       <c r="DE97" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DF97" t="n">
         <v>2.25</v>
@@ -45619,7 +45619,7 @@
         <v>3.08</v>
       </c>
       <c r="DO97" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP97" t="b">
         <v>1</v>
@@ -50226,7 +50226,7 @@
         <v>50</v>
       </c>
       <c r="DD107" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE107" t="n">
         <v>2.44</v>
@@ -50259,7 +50259,7 @@
         <v>3.08</v>
       </c>
       <c r="DO107" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP107" t="b">
         <v>1</v>
@@ -51155,7 +51155,7 @@
         <v>3.88</v>
       </c>
       <c r="DO109" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP109" t="b">
         <v>1</v>
@@ -52971,7 +52971,7 @@
         <v>2.35</v>
       </c>
       <c r="DO113" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP113" t="b">
         <v>0</v>
@@ -54309,7 +54309,7 @@
         <v>1.1</v>
       </c>
       <c r="DE116" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DF116" t="n">
         <v>1.17</v>
@@ -54339,7 +54339,7 @@
         <v>3.01</v>
       </c>
       <c r="DO116" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP116" t="b">
         <v>1</v>
@@ -55722,7 +55722,7 @@
         <v>52</v>
       </c>
       <c r="DD119" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE119" t="n">
         <v>0.5</v>
@@ -55755,7 +55755,7 @@
         <v>2.21</v>
       </c>
       <c r="DO119" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP119" t="b">
         <v>1</v>
@@ -59491,7 +59491,7 @@
         <v>4.17</v>
       </c>
       <c r="DO127" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP127" t="b">
         <v>1</v>
@@ -61313,7 +61313,7 @@
         <v>1.4</v>
       </c>
       <c r="DE131" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DF131" t="n">
         <v>1</v>
@@ -61343,7 +61343,7 @@
         <v>3.02</v>
       </c>
       <c r="DO131" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP131" t="b">
         <v>1</v>
@@ -62230,7 +62230,7 @@
         <v>65</v>
       </c>
       <c r="DD133" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE133" t="n">
         <v>1.1</v>
@@ -62263,7 +62263,7 @@
         <v>2.46</v>
       </c>
       <c r="DO133" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP133" t="b">
         <v>0</v>
@@ -66415,7 +66415,7 @@
         <v>2.06</v>
       </c>
       <c r="DO142" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP142" t="b">
         <v>1</v>
@@ -66535,170 +66535,162 @@
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>Samsunspor</t>
+          <t>Trabzonspor</t>
         </is>
       </c>
       <c r="E143" t="inlineStr">
         <is>
-          <t>İstanbul Başakşehir</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="F143" s="2" t="n">
         <v>46005.70833333334</v>
       </c>
       <c r="G143" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="H143" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="I143" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="J143" t="n">
         <v>7</v>
       </c>
       <c r="K143" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="L143" t="n">
+        <v>8</v>
+      </c>
+      <c r="M143" t="n">
+        <v>2</v>
+      </c>
+      <c r="N143" t="n">
+        <v>5</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0</v>
+      </c>
+      <c r="P143" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>13</v>
+      </c>
+      <c r="R143" t="n">
+        <v>5</v>
+      </c>
+      <c r="S143" t="n">
+        <v>21</v>
+      </c>
+      <c r="T143" t="n">
+        <v>4</v>
+      </c>
+      <c r="U143" t="n">
+        <v>34</v>
+      </c>
+      <c r="V143" t="n">
         <v>9</v>
       </c>
-      <c r="M143" t="n">
-        <v>0</v>
-      </c>
-      <c r="N143" t="n">
-        <v>0</v>
-      </c>
-      <c r="O143" t="n">
-        <v>0</v>
-      </c>
-      <c r="P143" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q143" t="n">
-        <v>4</v>
-      </c>
-      <c r="R143" t="n">
-        <v>6</v>
-      </c>
-      <c r="S143" t="n">
-        <v>11</v>
-      </c>
-      <c r="T143" t="n">
-        <v>6</v>
-      </c>
-      <c r="U143" t="n">
-        <v>15</v>
-      </c>
-      <c r="V143" t="n">
-        <v>12</v>
-      </c>
       <c r="W143" t="n">
-        <v>17</v>
+        <v>7</v>
       </c>
       <c r="X143" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="Y143" t="n">
-        <v>53</v>
+        <v>76</v>
       </c>
       <c r="Z143" t="n">
-        <v>47</v>
-      </c>
-      <c r="AA143" t="inlineStr">
-        <is>
-          <t>Stadyum Samsun</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>Sanayi Mahallesi, Tekkeköy, Samsun</t>
-        </is>
-      </c>
+        <v>24</v>
+      </c>
+      <c r="AA143" t="inlineStr"/>
+      <c r="AB143" t="inlineStr"/>
       <c r="AC143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AD143" t="n">
-        <v>0</v>
+        <v>7</v>
       </c>
       <c r="AE143" t="n">
-        <v>2.01</v>
+        <v>2.7</v>
       </c>
       <c r="AF143" t="n">
-        <v>3.58</v>
+        <v>3.4</v>
       </c>
       <c r="AG143" t="n">
-        <v>3.6</v>
+        <v>2.45</v>
       </c>
       <c r="AH143" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AI143" t="n">
-        <v>1.7</v>
+        <v>1.73</v>
       </c>
       <c r="AJ143" t="n">
-        <v>2.61</v>
+        <v>2.64</v>
       </c>
       <c r="AK143" t="n">
-        <v>1.62</v>
+        <v>1.6</v>
       </c>
       <c r="AL143" t="n">
-        <v>2.15</v>
+        <v>2.42</v>
       </c>
       <c r="AM143" t="n">
-        <v>1.44</v>
+        <v>1.42</v>
       </c>
       <c r="AN143" t="n">
-        <v>1.78</v>
+        <v>2</v>
       </c>
       <c r="AO143" t="n">
-        <v>2.44</v>
+        <v>2.53</v>
       </c>
       <c r="AP143" t="n">
-        <v>1.91</v>
+        <v>1.84</v>
       </c>
       <c r="AQ143" t="n">
-        <v>1.36</v>
+        <v>1.35</v>
       </c>
       <c r="AR143" t="n">
-        <v>2.45</v>
+        <v>2.4</v>
       </c>
       <c r="AS143" t="n">
-        <v>3.02</v>
+        <v>3.04</v>
       </c>
       <c r="AT143" t="n">
         <v>1.47</v>
       </c>
       <c r="AU143" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="AV143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW143" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="AX143" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AY143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AZ143" t="n">
         <v>2</v>
       </c>
       <c r="BA143" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BB143" t="n">
-        <v>196</v>
+        <v>-1</v>
       </c>
       <c r="BC143" t="n">
         <v>0</v>
       </c>
       <c r="BD143" t="n">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="BE143" t="n">
         <v>0</v>
@@ -66710,67 +66702,67 @@
         <v>2</v>
       </c>
       <c r="BH143" t="n">
-        <v>-1</v>
+        <v>1</v>
       </c>
       <c r="BI143" t="n">
         <v>2</v>
       </c>
       <c r="BJ143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="BK143" t="n">
         <v>5</v>
       </c>
       <c r="BL143" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BM143" t="n">
+        <v>2</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>1</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>3</v>
+      </c>
+      <c r="BS143" t="n">
         <v>4</v>
       </c>
-      <c r="BN143" t="n">
-        <v>5</v>
-      </c>
-      <c r="BO143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BP143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BQ143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BR143" t="n">
-        <v>0</v>
-      </c>
-      <c r="BS143" t="n">
-        <v>0</v>
-      </c>
       <c r="BT143" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="BU143" t="n">
         <v>1</v>
       </c>
       <c r="BV143" t="n">
-        <v>50</v>
+        <v>126</v>
       </c>
       <c r="BW143" t="n">
-        <v>44</v>
+        <v>9</v>
       </c>
       <c r="BX143" t="n">
-        <v>82</v>
+        <v>157</v>
       </c>
       <c r="BY143" t="n">
-        <v>113</v>
+        <v>38</v>
       </c>
       <c r="BZ143" t="n">
-        <v>1.58</v>
+        <v>3.95</v>
       </c>
       <c r="CA143" t="n">
-        <v>1.51</v>
+        <v>0.98</v>
       </c>
       <c r="CB143" t="n">
-        <v>3.09</v>
+        <v>4.93</v>
       </c>
       <c r="CC143" t="n">
         <v>0</v>
@@ -66803,88 +66795,88 @@
         <v>0</v>
       </c>
       <c r="CM143" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CN143" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="CO143" t="n">
-        <v>-1</v>
+        <v>0</v>
       </c>
       <c r="CP143" t="n">
-        <v>-1</v>
+        <v>2</v>
       </c>
       <c r="CQ143" t="n">
         <v>1</v>
       </c>
       <c r="CR143" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="CS143" t="n">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="CT143" t="n">
         <v>1</v>
       </c>
       <c r="CU143" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="CV143" t="n">
+        <v>7</v>
+      </c>
+      <c r="CW143" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX143" t="n">
+        <v>4</v>
+      </c>
+      <c r="CY143" t="n">
         <v>17</v>
       </c>
-      <c r="CW143" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX143" t="n">
-        <v>9</v>
-      </c>
-      <c r="CY143" t="n">
-        <v>5</v>
-      </c>
       <c r="CZ143" t="n">
-        <v>51</v>
+        <v>32</v>
       </c>
       <c r="DA143" t="n">
-        <v>69</v>
+        <v>88</v>
       </c>
       <c r="DB143" t="n">
-        <v>26</v>
+        <v>32</v>
       </c>
       <c r="DC143" t="n">
-        <v>63</v>
+        <v>94</v>
       </c>
       <c r="DD143" t="n">
-        <v>1.4</v>
+        <v>2.2</v>
       </c>
       <c r="DE143" t="n">
         <v>1.6</v>
       </c>
       <c r="DF143" t="n">
-        <v>1.63</v>
+        <v>2.25</v>
       </c>
       <c r="DG143" t="n">
-        <v>1.25</v>
+        <v>1.75</v>
       </c>
       <c r="DH143" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DI143" t="n">
         <v>1.67</v>
       </c>
-      <c r="DI143" t="n">
-        <v>1.13</v>
-      </c>
       <c r="DJ143" t="n">
-        <v>51</v>
+        <v>69</v>
       </c>
       <c r="DK143" t="n">
-        <v>32</v>
+        <v>13</v>
       </c>
       <c r="DL143" t="n">
-        <v>1.5</v>
+        <v>1.78</v>
       </c>
       <c r="DM143" t="n">
-        <v>1.49</v>
+        <v>1.65</v>
       </c>
       <c r="DN143" t="n">
-        <v>2.99</v>
+        <v>3.43</v>
       </c>
       <c r="DO143" t="n">
         <v>20</v>
@@ -66896,98 +66888,82 @@
         <v>1</v>
       </c>
       <c r="DR143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DU143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DV143" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW143" t="inlineStr">
         <is>
-          <t>1.81</t>
+          <t>1.74</t>
         </is>
       </c>
       <c r="DX143" t="inlineStr">
         <is>
-          <t>3.06</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="DY143" t="inlineStr">
         <is>
-          <t>1.25</t>
+          <t>1.22</t>
         </is>
       </c>
       <c r="DZ143" t="inlineStr">
         <is>
-          <t>2.80</t>
+          <t>2.65</t>
         </is>
       </c>
       <c r="EA143" t="inlineStr">
         <is>
-          <t>1.46</t>
+          <t>1.51</t>
         </is>
       </c>
       <c r="EB143" t="inlineStr">
         <is>
-          <t>1.37</t>
+          <t>1.35</t>
         </is>
       </c>
       <c r="EC143" t="inlineStr">
         <is>
-          <t>3.21</t>
-        </is>
-      </c>
-      <c r="ED143" t="inlineStr">
-        <is>
-          <t>1.50</t>
-        </is>
-      </c>
-      <c r="EE143" t="inlineStr">
-        <is>
-          <t>1.94</t>
-        </is>
-      </c>
-      <c r="EF143" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="EG143" t="inlineStr">
-        <is>
-          <t>1.88</t>
-        </is>
-      </c>
+          <t>3.36</t>
+        </is>
+      </c>
+      <c r="ED143" t="inlineStr"/>
+      <c r="EE143" t="inlineStr"/>
+      <c r="EF143" t="inlineStr"/>
+      <c r="EG143" t="inlineStr"/>
       <c r="EH143" t="inlineStr">
         <is>
-          <t>3.78</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="EI143" t="inlineStr">
         <is>
-          <t>2.08</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="EJ143" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>3.51</t>
         </is>
       </c>
       <c r="EK143" t="inlineStr">
         <is>
-          <t>1.66</t>
+          <t>1.60</t>
         </is>
       </c>
       <c r="EL143" t="inlineStr">
         <is>
-          <t>2.29</t>
+          <t>2.41</t>
         </is>
       </c>
     </row>
@@ -67007,162 +66983,170 @@
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>Trabzonspor</t>
+          <t>Samsunspor</t>
         </is>
       </c>
       <c r="E144" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>İstanbul Başakşehir</t>
         </is>
       </c>
       <c r="F144" s="2" t="n">
         <v>46005.70833333334</v>
       </c>
       <c r="G144" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H144" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I144" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="J144" t="n">
         <v>7</v>
       </c>
       <c r="K144" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="L144" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="M144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="N144" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="O144" t="n">
         <v>0</v>
       </c>
       <c r="P144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q144" t="n">
-        <v>13</v>
+        <v>4</v>
       </c>
       <c r="R144" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S144" t="n">
-        <v>21</v>
+        <v>11</v>
       </c>
       <c r="T144" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="U144" t="n">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c r="V144" t="n">
+        <v>12</v>
+      </c>
+      <c r="W144" t="n">
+        <v>17</v>
+      </c>
+      <c r="X144" t="n">
         <v>9</v>
       </c>
-      <c r="W144" t="n">
-        <v>7</v>
-      </c>
-      <c r="X144" t="n">
-        <v>8</v>
-      </c>
       <c r="Y144" t="n">
-        <v>76</v>
+        <v>53</v>
       </c>
       <c r="Z144" t="n">
-        <v>24</v>
-      </c>
-      <c r="AA144" t="inlineStr"/>
-      <c r="AB144" t="inlineStr"/>
+        <v>47</v>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>Stadyum Samsun</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>Sanayi Mahallesi, Tekkeköy, Samsun</t>
+        </is>
+      </c>
       <c r="AC144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AD144" t="n">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c r="AE144" t="n">
-        <v>2.7</v>
+        <v>2.01</v>
       </c>
       <c r="AF144" t="n">
-        <v>3.4</v>
+        <v>3.58</v>
       </c>
       <c r="AG144" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="AH144" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AI144" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="AJ144" t="n">
+        <v>2.61</v>
+      </c>
+      <c r="AK144" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AL144" t="n">
+        <v>2.15</v>
+      </c>
+      <c r="AM144" t="n">
+        <v>1.44</v>
+      </c>
+      <c r="AN144" t="n">
+        <v>1.78</v>
+      </c>
+      <c r="AO144" t="n">
+        <v>2.44</v>
+      </c>
+      <c r="AP144" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AQ144" t="n">
+        <v>1.36</v>
+      </c>
+      <c r="AR144" t="n">
         <v>2.45</v>
       </c>
-      <c r="AH144" t="n">
-        <v>1.18</v>
-      </c>
-      <c r="AI144" t="n">
-        <v>1.73</v>
-      </c>
-      <c r="AJ144" t="n">
-        <v>2.64</v>
-      </c>
-      <c r="AK144" t="n">
-        <v>1.6</v>
-      </c>
-      <c r="AL144" t="n">
-        <v>2.42</v>
-      </c>
-      <c r="AM144" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AN144" t="n">
-        <v>2</v>
-      </c>
-      <c r="AO144" t="n">
-        <v>2.53</v>
-      </c>
-      <c r="AP144" t="n">
-        <v>1.84</v>
-      </c>
-      <c r="AQ144" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="AR144" t="n">
-        <v>2.4</v>
-      </c>
       <c r="AS144" t="n">
-        <v>3.04</v>
+        <v>3.02</v>
       </c>
       <c r="AT144" t="n">
         <v>1.47</v>
       </c>
       <c r="AU144" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="AV144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW144" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="AX144" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AY144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="AZ144" t="n">
         <v>2</v>
       </c>
       <c r="BA144" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BB144" t="n">
-        <v>-1</v>
+        <v>196</v>
       </c>
       <c r="BC144" t="n">
         <v>0</v>
       </c>
       <c r="BD144" t="n">
-        <v>44</v>
+        <v>57</v>
       </c>
       <c r="BE144" t="n">
         <v>0</v>
@@ -67174,181 +67158,181 @@
         <v>2</v>
       </c>
       <c r="BH144" t="n">
-        <v>1</v>
+        <v>-1</v>
       </c>
       <c r="BI144" t="n">
         <v>2</v>
       </c>
       <c r="BJ144" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="BK144" t="n">
         <v>5</v>
       </c>
       <c r="BL144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BM144" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BN144" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="BO144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP144" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BQ144" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BR144" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="BS144" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BT144" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="BU144" t="n">
         <v>1</v>
       </c>
       <c r="BV144" t="n">
-        <v>126</v>
+        <v>50</v>
       </c>
       <c r="BW144" t="n">
+        <v>44</v>
+      </c>
+      <c r="BX144" t="n">
+        <v>82</v>
+      </c>
+      <c r="BY144" t="n">
+        <v>113</v>
+      </c>
+      <c r="BZ144" t="n">
+        <v>1.58</v>
+      </c>
+      <c r="CA144" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="CB144" t="n">
+        <v>3.09</v>
+      </c>
+      <c r="CC144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL144" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CN144" t="n">
+        <v>2</v>
+      </c>
+      <c r="CO144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CP144" t="n">
+        <v>-1</v>
+      </c>
+      <c r="CQ144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR144" t="n">
+        <v>15</v>
+      </c>
+      <c r="CS144" t="n">
+        <v>24</v>
+      </c>
+      <c r="CT144" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU144" t="n">
         <v>9</v>
       </c>
-      <c r="BX144" t="n">
-        <v>157</v>
-      </c>
-      <c r="BY144" t="n">
-        <v>38</v>
-      </c>
-      <c r="BZ144" t="n">
-        <v>3.95</v>
-      </c>
-      <c r="CA144" t="n">
-        <v>0.98</v>
-      </c>
-      <c r="CB144" t="n">
-        <v>4.93</v>
-      </c>
-      <c r="CC144" t="n">
-        <v>0</v>
-      </c>
-      <c r="CD144" t="n">
-        <v>0</v>
-      </c>
-      <c r="CE144" t="n">
-        <v>0</v>
-      </c>
-      <c r="CF144" t="n">
-        <v>0</v>
-      </c>
-      <c r="CG144" t="n">
-        <v>0</v>
-      </c>
-      <c r="CH144" t="n">
-        <v>0</v>
-      </c>
-      <c r="CI144" t="n">
-        <v>1</v>
-      </c>
-      <c r="CJ144" t="n">
-        <v>1</v>
-      </c>
-      <c r="CK144" t="n">
-        <v>0</v>
-      </c>
-      <c r="CL144" t="n">
-        <v>0</v>
-      </c>
-      <c r="CM144" t="n">
-        <v>0</v>
-      </c>
-      <c r="CN144" t="n">
-        <v>0</v>
-      </c>
-      <c r="CO144" t="n">
-        <v>0</v>
-      </c>
-      <c r="CP144" t="n">
-        <v>2</v>
-      </c>
-      <c r="CQ144" t="n">
-        <v>1</v>
-      </c>
-      <c r="CR144" t="n">
-        <v>29</v>
-      </c>
-      <c r="CS144" t="n">
-        <v>14</v>
-      </c>
-      <c r="CT144" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU144" t="n">
-        <v>8</v>
-      </c>
       <c r="CV144" t="n">
-        <v>7</v>
+        <v>17</v>
       </c>
       <c r="CW144" t="n">
         <v>1</v>
       </c>
       <c r="CX144" t="n">
-        <v>4</v>
+        <v>9</v>
       </c>
       <c r="CY144" t="n">
-        <v>17</v>
+        <v>5</v>
       </c>
       <c r="CZ144" t="n">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="DA144" t="n">
-        <v>88</v>
+        <v>69</v>
       </c>
       <c r="DB144" t="n">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="DC144" t="n">
-        <v>94</v>
+        <v>63</v>
       </c>
       <c r="DD144" t="n">
-        <v>2.2</v>
+        <v>1.4</v>
       </c>
       <c r="DE144" t="n">
         <v>1.6</v>
       </c>
       <c r="DF144" t="n">
-        <v>2.25</v>
+        <v>1.63</v>
       </c>
       <c r="DG144" t="n">
-        <v>1.75</v>
+        <v>1.25</v>
       </c>
       <c r="DH144" t="n">
-        <v>2.27</v>
+        <v>1.67</v>
       </c>
       <c r="DI144" t="n">
-        <v>1.67</v>
+        <v>1.13</v>
       </c>
       <c r="DJ144" t="n">
-        <v>69</v>
+        <v>51</v>
       </c>
       <c r="DK144" t="n">
-        <v>13</v>
+        <v>32</v>
       </c>
       <c r="DL144" t="n">
-        <v>1.78</v>
+        <v>1.5</v>
       </c>
       <c r="DM144" t="n">
-        <v>1.65</v>
+        <v>1.49</v>
       </c>
       <c r="DN144" t="n">
-        <v>3.43</v>
+        <v>2.99</v>
       </c>
       <c r="DO144" t="n">
         <v>20</v>
@@ -67360,82 +67344,98 @@
         <v>1</v>
       </c>
       <c r="DR144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DU144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DV144" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW144" t="inlineStr">
         <is>
-          <t>1.74</t>
+          <t>1.81</t>
         </is>
       </c>
       <c r="DX144" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.06</t>
         </is>
       </c>
       <c r="DY144" t="inlineStr">
         <is>
-          <t>1.22</t>
+          <t>1.25</t>
         </is>
       </c>
       <c r="DZ144" t="inlineStr">
         <is>
-          <t>2.65</t>
+          <t>2.80</t>
         </is>
       </c>
       <c r="EA144" t="inlineStr">
         <is>
-          <t>1.51</t>
+          <t>1.46</t>
         </is>
       </c>
       <c r="EB144" t="inlineStr">
         <is>
-          <t>1.35</t>
+          <t>1.37</t>
         </is>
       </c>
       <c r="EC144" t="inlineStr">
         <is>
-          <t>3.36</t>
-        </is>
-      </c>
-      <c r="ED144" t="inlineStr"/>
-      <c r="EE144" t="inlineStr"/>
-      <c r="EF144" t="inlineStr"/>
-      <c r="EG144" t="inlineStr"/>
+          <t>3.21</t>
+        </is>
+      </c>
+      <c r="ED144" t="inlineStr">
+        <is>
+          <t>1.50</t>
+        </is>
+      </c>
+      <c r="EE144" t="inlineStr">
+        <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="EF144" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="EG144" t="inlineStr">
+        <is>
+          <t>1.88</t>
+        </is>
+      </c>
       <c r="EH144" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>3.78</t>
         </is>
       </c>
       <c r="EI144" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.08</t>
         </is>
       </c>
       <c r="EJ144" t="inlineStr">
         <is>
-          <t>3.51</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="EK144" t="inlineStr">
         <is>
-          <t>1.60</t>
+          <t>1.66</t>
         </is>
       </c>
       <c r="EL144" t="inlineStr">
         <is>
-          <t>2.41</t>
+          <t>2.29</t>
         </is>
       </c>
     </row>
@@ -67807,7 +67807,7 @@
         <v>3.77</v>
       </c>
       <c r="DO145" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP145" t="b">
         <v>1</v>
@@ -68214,7 +68214,7 @@
         <v>38</v>
       </c>
       <c r="DD146" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE146" t="n">
         <v>1.2</v>
@@ -68247,7 +68247,7 @@
         <v>2.07</v>
       </c>
       <c r="DO146" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP146" t="b">
         <v>1</v>
@@ -69113,7 +69113,7 @@
         <v>1</v>
       </c>
       <c r="DE148" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DF148" t="n">
         <v>1.13</v>
@@ -69143,7 +69143,7 @@
         <v>3.06</v>
       </c>
       <c r="DO148" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP148" t="b">
         <v>1</v>
@@ -74174,7 +74174,7 @@
         <v>54</v>
       </c>
       <c r="DD159" t="n">
-        <v>1.8</v>
+        <v>1.64</v>
       </c>
       <c r="DE159" t="n">
         <v>2</v>
@@ -74207,7 +74207,7 @@
         <v>2.73</v>
       </c>
       <c r="DO159" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP159" t="b">
         <v>1</v>
@@ -74649,7 +74649,7 @@
         <v>1.2</v>
       </c>
       <c r="DE160" t="n">
-        <v>2.2</v>
+        <v>2.27</v>
       </c>
       <c r="DF160" t="n">
         <v>1.5</v>
@@ -74679,7 +74679,7 @@
         <v>3.17</v>
       </c>
       <c r="DO160" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP160" t="b">
         <v>1</v>
@@ -75223,162 +75223,162 @@
       </c>
       <c r="D162" t="inlineStr">
         <is>
-          <t>Göztepe</t>
+          <t>Beşiktaş</t>
         </is>
       </c>
       <c r="E162" t="inlineStr">
         <is>
-          <t>Rizespor</t>
+          <t>Kayserispor</t>
         </is>
       </c>
       <c r="F162" s="2" t="n">
         <v>46041.70833333334</v>
       </c>
       <c r="G162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="H162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I162" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="J162" t="n">
-        <v>3</v>
+        <v>9</v>
       </c>
       <c r="K162" t="n">
+        <v>2</v>
+      </c>
+      <c r="L162" t="n">
+        <v>11</v>
+      </c>
+      <c r="M162" t="n">
+        <v>2</v>
+      </c>
+      <c r="N162" t="n">
+        <v>3</v>
+      </c>
+      <c r="O162" t="n">
+        <v>0</v>
+      </c>
+      <c r="P162" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q162" t="n">
         <v>9</v>
       </c>
-      <c r="L162" t="n">
+      <c r="R162" t="n">
+        <v>3</v>
+      </c>
+      <c r="S162" t="n">
+        <v>22</v>
+      </c>
+      <c r="T162" t="n">
+        <v>6</v>
+      </c>
+      <c r="U162" t="n">
+        <v>31</v>
+      </c>
+      <c r="V162" t="n">
+        <v>9</v>
+      </c>
+      <c r="W162" t="n">
         <v>12</v>
       </c>
-      <c r="M162" t="n">
-        <v>3</v>
-      </c>
-      <c r="N162" t="n">
-        <v>1</v>
-      </c>
-      <c r="O162" t="n">
-        <v>0</v>
-      </c>
-      <c r="P162" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q162" t="n">
-        <v>7</v>
-      </c>
-      <c r="R162" t="n">
-        <v>5</v>
-      </c>
-      <c r="S162" t="n">
-        <v>6</v>
-      </c>
-      <c r="T162" t="n">
-        <v>11</v>
-      </c>
-      <c r="U162" t="n">
-        <v>13</v>
-      </c>
-      <c r="V162" t="n">
-        <v>16</v>
-      </c>
-      <c r="W162" t="n">
+      <c r="X162" t="n">
         <v>15</v>
       </c>
-      <c r="X162" t="n">
-        <v>8</v>
-      </c>
       <c r="Y162" t="n">
-        <v>33</v>
+        <v>69</v>
       </c>
       <c r="Z162" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="AA162" t="inlineStr"/>
       <c r="AB162" t="inlineStr"/>
       <c r="AC162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AD162" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="AE162" t="n">
-        <v>1.93</v>
+        <v>1.33</v>
       </c>
       <c r="AF162" t="n">
-        <v>3.1</v>
+        <v>5</v>
       </c>
       <c r="AG162" t="n">
-        <v>3.8</v>
+        <v>6.9</v>
       </c>
       <c r="AH162" t="n">
-        <v>1.34</v>
+        <v>1.13</v>
       </c>
       <c r="AI162" t="n">
-        <v>2.17</v>
+        <v>1.4</v>
       </c>
       <c r="AJ162" t="n">
-        <v>3.9</v>
+        <v>2.14</v>
       </c>
       <c r="AK162" t="n">
-        <v>1.93</v>
+        <v>1.68</v>
       </c>
       <c r="AL162" t="n">
-        <v>1.76</v>
+        <v>2.24</v>
       </c>
       <c r="AM162" t="n">
-        <v>1.55</v>
+        <v>1.41</v>
       </c>
       <c r="AN162" t="n">
-        <v>2.17</v>
+        <v>1.77</v>
       </c>
       <c r="AO162" t="n">
-        <v>2.22</v>
+        <v>2.7</v>
       </c>
       <c r="AP162" t="n">
-        <v>1.81</v>
+        <v>2.06</v>
       </c>
       <c r="AQ162" t="n">
-        <v>1.47</v>
+        <v>1.22</v>
       </c>
       <c r="AR162" t="n">
-        <v>3.04</v>
+        <v>2.14</v>
       </c>
       <c r="AS162" t="n">
-        <v>2.83</v>
+        <v>3.85</v>
       </c>
       <c r="AT162" t="n">
-        <v>1.33</v>
+        <v>1.66</v>
       </c>
       <c r="AU162" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="AV162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AW162" t="n">
         <v>0</v>
       </c>
       <c r="AX162" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AY162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="AZ162" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="BA162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BB162" t="n">
-        <v>357</v>
+        <v>109</v>
       </c>
       <c r="BC162" t="n">
         <v>0</v>
       </c>
       <c r="BD162" t="n">
-        <v>50</v>
+        <v>83</v>
       </c>
       <c r="BE162" t="n">
         <v>0</v>
@@ -75393,76 +75393,76 @@
         <v>1</v>
       </c>
       <c r="BI162" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="BJ162" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BK162" t="n">
-        <v>1</v>
+        <v>5</v>
       </c>
       <c r="BL162" t="n">
+        <v>0</v>
+      </c>
+      <c r="BM162" t="n">
         <v>6</v>
       </c>
-      <c r="BM162" t="n">
+      <c r="BN162" t="n">
         <v>5</v>
       </c>
-      <c r="BN162" t="n">
-        <v>7</v>
-      </c>
       <c r="BO162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BP162" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BQ162" t="n">
         <v>2</v>
       </c>
       <c r="BR162" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BS162" t="n">
         <v>2</v>
       </c>
       <c r="BT162" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BU162" t="n">
         <v>1</v>
       </c>
       <c r="BV162" t="n">
-        <v>25</v>
+        <v>83</v>
       </c>
       <c r="BW162" t="n">
-        <v>46</v>
+        <v>23</v>
       </c>
       <c r="BX162" t="n">
-        <v>85</v>
+        <v>163</v>
       </c>
       <c r="BY162" t="n">
-        <v>94</v>
+        <v>62</v>
       </c>
       <c r="BZ162" t="n">
-        <v>1.5</v>
+        <v>3.18</v>
       </c>
       <c r="CA162" t="n">
-        <v>1.69</v>
+        <v>0.95</v>
       </c>
       <c r="CB162" t="n">
-        <v>3.19</v>
+        <v>4.13</v>
       </c>
       <c r="CC162" t="n">
         <v>0</v>
       </c>
       <c r="CD162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CE162" t="n">
         <v>0</v>
       </c>
       <c r="CF162" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="CG162" t="n">
         <v>0</v>
@@ -75501,70 +75501,70 @@
         <v>15</v>
       </c>
       <c r="CS162" t="n">
+        <v>10</v>
+      </c>
+      <c r="CT162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU162" t="n">
+        <v>15</v>
+      </c>
+      <c r="CV162" t="n">
+        <v>12</v>
+      </c>
+      <c r="CW162" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX162" t="n">
+        <v>6</v>
+      </c>
+      <c r="CY162" t="n">
         <v>16</v>
       </c>
-      <c r="CT162" t="n">
-        <v>1</v>
-      </c>
-      <c r="CU162" t="n">
-        <v>8</v>
-      </c>
-      <c r="CV162" t="n">
-        <v>14</v>
-      </c>
-      <c r="CW162" t="n">
-        <v>1</v>
-      </c>
-      <c r="CX162" t="n">
-        <v>8</v>
-      </c>
-      <c r="CY162" t="n">
-        <v>6</v>
-      </c>
       <c r="CZ162" t="n">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="DA162" t="n">
-        <v>63</v>
+        <v>89</v>
       </c>
       <c r="DB162" t="n">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="DC162" t="n">
-        <v>63</v>
+        <v>47</v>
       </c>
       <c r="DD162" t="n">
-        <v>2.1</v>
+        <v>2</v>
       </c>
       <c r="DE162" t="n">
-        <v>0.9</v>
+        <v>0.82</v>
       </c>
       <c r="DF162" t="n">
-        <v>1.88</v>
+        <v>1.75</v>
       </c>
       <c r="DG162" t="n">
         <v>1</v>
       </c>
       <c r="DH162" t="n">
-        <v>1.88</v>
+        <v>1.71</v>
       </c>
       <c r="DI162" t="n">
-        <v>1.06</v>
+        <v>0.88</v>
       </c>
       <c r="DJ162" t="n">
-        <v>69</v>
+        <v>46</v>
       </c>
       <c r="DK162" t="n">
-        <v>38</v>
+        <v>12</v>
       </c>
       <c r="DL162" t="n">
-        <v>1.41</v>
+        <v>1.78</v>
       </c>
       <c r="DM162" t="n">
-        <v>1.1</v>
+        <v>1.3</v>
       </c>
       <c r="DN162" t="n">
-        <v>2.51</v>
+        <v>3.08</v>
       </c>
       <c r="DO162" t="n">
         <v>20</v>
@@ -75573,13 +75573,13 @@
         <v>1</v>
       </c>
       <c r="DQ162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DR162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DS162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DT162" t="b">
         <v>0</v>
@@ -75588,86 +75588,62 @@
         <v>0</v>
       </c>
       <c r="DV162" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="DW162" t="inlineStr">
         <is>
-          <t>2.44</t>
+          <t>1.43</t>
         </is>
       </c>
       <c r="DX162" t="inlineStr">
         <is>
-          <t>4.54</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="DY162" t="inlineStr">
         <is>
-          <t>1.45</t>
-        </is>
-      </c>
-      <c r="DZ162" t="inlineStr">
-        <is>
-          <t>3.26</t>
-        </is>
-      </c>
-      <c r="EA162" t="inlineStr">
-        <is>
-          <t>1.36</t>
-        </is>
-      </c>
-      <c r="EB162" t="inlineStr">
-        <is>
-          <t>1.52</t>
-        </is>
-      </c>
-      <c r="EC162" t="inlineStr">
-        <is>
-          <t>2.62</t>
-        </is>
-      </c>
-      <c r="ED162" t="inlineStr">
-        <is>
-          <t>1.57</t>
-        </is>
-      </c>
+          <t>1.14</t>
+        </is>
+      </c>
+      <c r="DZ162" t="inlineStr"/>
+      <c r="EA162" t="inlineStr"/>
+      <c r="EB162" t="inlineStr"/>
+      <c r="EC162" t="inlineStr"/>
+      <c r="ED162" t="inlineStr"/>
       <c r="EE162" t="inlineStr">
         <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="EF162" t="inlineStr">
-        <is>
-          <t>2.29</t>
-        </is>
-      </c>
+          <t>2.04</t>
+        </is>
+      </c>
+      <c r="EF162" t="inlineStr"/>
       <c r="EG162" t="inlineStr">
         <is>
-          <t>1.99</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="EH162" t="inlineStr">
         <is>
-          <t>4.25</t>
+          <t>7.48</t>
         </is>
       </c>
       <c r="EI162" t="inlineStr">
         <is>
-          <t>2.13</t>
+          <t>1.39</t>
         </is>
       </c>
       <c r="EJ162" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="EK162" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>1.64</t>
         </is>
       </c>
       <c r="EL162" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>2.33</t>
         </is>
       </c>
     </row>
@@ -75687,162 +75663,162 @@
       </c>
       <c r="D163" t="inlineStr">
         <is>
-          <t>Beşiktaş</t>
+          <t>Göztepe</t>
         </is>
       </c>
       <c r="E163" t="inlineStr">
         <is>
-          <t>Kayserispor</t>
+          <t>Rizespor</t>
         </is>
       </c>
       <c r="F163" s="2" t="n">
         <v>46041.70833333334</v>
       </c>
       <c r="G163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I163" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="J163" t="n">
+        <v>3</v>
+      </c>
+      <c r="K163" t="n">
         <v>9</v>
       </c>
-      <c r="K163" t="n">
-        <v>2</v>
-      </c>
       <c r="L163" t="n">
+        <v>12</v>
+      </c>
+      <c r="M163" t="n">
+        <v>3</v>
+      </c>
+      <c r="N163" t="n">
+        <v>1</v>
+      </c>
+      <c r="O163" t="n">
+        <v>0</v>
+      </c>
+      <c r="P163" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q163" t="n">
+        <v>7</v>
+      </c>
+      <c r="R163" t="n">
+        <v>5</v>
+      </c>
+      <c r="S163" t="n">
+        <v>6</v>
+      </c>
+      <c r="T163" t="n">
         <v>11</v>
       </c>
-      <c r="M163" t="n">
-        <v>2</v>
-      </c>
-      <c r="N163" t="n">
-        <v>3</v>
-      </c>
-      <c r="O163" t="n">
-        <v>0</v>
-      </c>
-      <c r="P163" t="n">
-        <v>0</v>
-      </c>
-      <c r="Q163" t="n">
-        <v>9</v>
-      </c>
-      <c r="R163" t="n">
-        <v>3</v>
-      </c>
-      <c r="S163" t="n">
-        <v>22</v>
-      </c>
-      <c r="T163" t="n">
-        <v>6</v>
-      </c>
       <c r="U163" t="n">
-        <v>31</v>
+        <v>13</v>
       </c>
       <c r="V163" t="n">
-        <v>9</v>
+        <v>16</v>
       </c>
       <c r="W163" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="X163" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="Y163" t="n">
-        <v>69</v>
+        <v>33</v>
       </c>
       <c r="Z163" t="n">
-        <v>31</v>
+        <v>67</v>
       </c>
       <c r="AA163" t="inlineStr"/>
       <c r="AB163" t="inlineStr"/>
       <c r="AC163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AD163" t="n">
-        <v>3</v>
+        <v>1</v>
       </c>
       <c r="AE163" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AF163" t="n">
+        <v>3.1</v>
+      </c>
+      <c r="AG163" t="n">
+        <v>3.8</v>
+      </c>
+      <c r="AH163" t="n">
+        <v>1.34</v>
+      </c>
+      <c r="AI163" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AJ163" t="n">
+        <v>3.9</v>
+      </c>
+      <c r="AK163" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="AL163" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="AM163" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="AN163" t="n">
+        <v>2.17</v>
+      </c>
+      <c r="AO163" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AP163" t="n">
+        <v>1.81</v>
+      </c>
+      <c r="AQ163" t="n">
+        <v>1.47</v>
+      </c>
+      <c r="AR163" t="n">
+        <v>3.04</v>
+      </c>
+      <c r="AS163" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="AT163" t="n">
         <v>1.33</v>
       </c>
-      <c r="AF163" t="n">
-        <v>5</v>
-      </c>
-      <c r="AG163" t="n">
-        <v>6.9</v>
-      </c>
-      <c r="AH163" t="n">
-        <v>1.13</v>
-      </c>
-      <c r="AI163" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AJ163" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AK163" t="n">
-        <v>1.68</v>
-      </c>
-      <c r="AL163" t="n">
-        <v>2.24</v>
-      </c>
-      <c r="AM163" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="AN163" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="AO163" t="n">
-        <v>2.7</v>
-      </c>
-      <c r="AP163" t="n">
-        <v>2.06</v>
-      </c>
-      <c r="AQ163" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AR163" t="n">
-        <v>2.14</v>
-      </c>
-      <c r="AS163" t="n">
-        <v>3.85</v>
-      </c>
-      <c r="AT163" t="n">
-        <v>1.66</v>
-      </c>
       <c r="AU163" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="AV163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AW163" t="n">
         <v>0</v>
       </c>
       <c r="AX163" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AY163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AZ163" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="BA163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BB163" t="n">
-        <v>109</v>
+        <v>357</v>
       </c>
       <c r="BC163" t="n">
         <v>0</v>
       </c>
       <c r="BD163" t="n">
-        <v>83</v>
+        <v>50</v>
       </c>
       <c r="BE163" t="n">
         <v>0</v>
@@ -75857,76 +75833,76 @@
         <v>1</v>
       </c>
       <c r="BI163" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="BJ163" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BK163" t="n">
+        <v>1</v>
+      </c>
+      <c r="BL163" t="n">
+        <v>6</v>
+      </c>
+      <c r="BM163" t="n">
         <v>5</v>
       </c>
-      <c r="BL163" t="n">
-        <v>0</v>
-      </c>
-      <c r="BM163" t="n">
-        <v>6</v>
-      </c>
       <c r="BN163" t="n">
-        <v>5</v>
+        <v>7</v>
       </c>
       <c r="BO163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="BP163" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="BQ163" t="n">
         <v>2</v>
       </c>
       <c r="BR163" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="BS163" t="n">
         <v>2</v>
       </c>
       <c r="BT163" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BU163" t="n">
         <v>1</v>
       </c>
       <c r="BV163" t="n">
-        <v>83</v>
+        <v>25</v>
       </c>
       <c r="BW163" t="n">
-        <v>23</v>
+        <v>46</v>
       </c>
       <c r="BX163" t="n">
-        <v>163</v>
+        <v>85</v>
       </c>
       <c r="BY163" t="n">
-        <v>62</v>
+        <v>94</v>
       </c>
       <c r="BZ163" t="n">
-        <v>3.18</v>
+        <v>1.5</v>
       </c>
       <c r="CA163" t="n">
-        <v>0.95</v>
+        <v>1.69</v>
       </c>
       <c r="CB163" t="n">
-        <v>4.13</v>
+        <v>3.19</v>
       </c>
       <c r="CC163" t="n">
         <v>0</v>
       </c>
       <c r="CD163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CE163" t="n">
         <v>0</v>
       </c>
       <c r="CF163" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="CG163" t="n">
         <v>0</v>
@@ -75965,70 +75941,70 @@
         <v>15</v>
       </c>
       <c r="CS163" t="n">
-        <v>10</v>
+        <v>16</v>
       </c>
       <c r="CT163" t="n">
         <v>1</v>
       </c>
       <c r="CU163" t="n">
-        <v>15</v>
+        <v>8</v>
       </c>
       <c r="CV163" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="CW163" t="n">
         <v>1</v>
       </c>
       <c r="CX163" t="n">
+        <v>8</v>
+      </c>
+      <c r="CY163" t="n">
         <v>6</v>
       </c>
-      <c r="CY163" t="n">
-        <v>16</v>
-      </c>
       <c r="CZ163" t="n">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="DA163" t="n">
-        <v>89</v>
+        <v>63</v>
       </c>
       <c r="DB163" t="n">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="DC163" t="n">
-        <v>47</v>
+        <v>63</v>
       </c>
       <c r="DD163" t="n">
-        <v>2</v>
+        <v>2.1</v>
       </c>
       <c r="DE163" t="n">
-        <v>0.82</v>
+        <v>0.9</v>
       </c>
       <c r="DF163" t="n">
-        <v>1.75</v>
+        <v>1.88</v>
       </c>
       <c r="DG163" t="n">
         <v>1</v>
       </c>
       <c r="DH163" t="n">
-        <v>1.71</v>
+        <v>1.88</v>
       </c>
       <c r="DI163" t="n">
-        <v>0.88</v>
+        <v>1.06</v>
       </c>
       <c r="DJ163" t="n">
-        <v>46</v>
+        <v>69</v>
       </c>
       <c r="DK163" t="n">
-        <v>12</v>
+        <v>38</v>
       </c>
       <c r="DL163" t="n">
-        <v>1.78</v>
+        <v>1.41</v>
       </c>
       <c r="DM163" t="n">
-        <v>1.3</v>
+        <v>1.1</v>
       </c>
       <c r="DN163" t="n">
-        <v>3.08</v>
+        <v>2.51</v>
       </c>
       <c r="DO163" t="n">
         <v>20</v>
@@ -76037,13 +76013,13 @@
         <v>1</v>
       </c>
       <c r="DQ163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DR163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DS163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DT163" t="b">
         <v>0</v>
@@ -76052,62 +76028,86 @@
         <v>0</v>
       </c>
       <c r="DV163" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="DW163" t="inlineStr">
         <is>
-          <t>1.43</t>
+          <t>2.44</t>
         </is>
       </c>
       <c r="DX163" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>4.54</t>
         </is>
       </c>
       <c r="DY163" t="inlineStr">
         <is>
-          <t>1.14</t>
-        </is>
-      </c>
-      <c r="DZ163" t="inlineStr"/>
-      <c r="EA163" t="inlineStr"/>
-      <c r="EB163" t="inlineStr"/>
-      <c r="EC163" t="inlineStr"/>
-      <c r="ED163" t="inlineStr"/>
+          <t>1.45</t>
+        </is>
+      </c>
+      <c r="DZ163" t="inlineStr">
+        <is>
+          <t>3.26</t>
+        </is>
+      </c>
+      <c r="EA163" t="inlineStr">
+        <is>
+          <t>1.36</t>
+        </is>
+      </c>
+      <c r="EB163" t="inlineStr">
+        <is>
+          <t>1.52</t>
+        </is>
+      </c>
+      <c r="EC163" t="inlineStr">
+        <is>
+          <t>2.62</t>
+        </is>
+      </c>
+      <c r="ED163" t="inlineStr">
+        <is>
+          <t>1.57</t>
+        </is>
+      </c>
       <c r="EE163" t="inlineStr">
         <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="EF163" t="inlineStr"/>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="EF163" t="inlineStr">
+        <is>
+          <t>2.29</t>
+        </is>
+      </c>
       <c r="EG163" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>1.99</t>
         </is>
       </c>
       <c r="EH163" t="inlineStr">
         <is>
-          <t>7.48</t>
+          <t>4.25</t>
         </is>
       </c>
       <c r="EI163" t="inlineStr">
         <is>
-          <t>1.39</t>
+          <t>2.13</t>
         </is>
       </c>
       <c r="EJ163" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="EK163" t="inlineStr">
         <is>
-          <t>1.64</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="EL163" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>1.82</t>
         </is>
       </c>
     </row>
@@ -77399,7 +77399,7 @@
         <v>2.59</v>
       </c>
       <c r="DO166" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP166" t="b">
         <v>0</v>
@@ -79711,7 +79711,7 @@
         <v>3.84</v>
       </c>
       <c r="DO171" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="DP171" t="b">
         <v>1</v>
@@ -81291,7 +81291,7 @@
         <v>13</v>
       </c>
       <c r="W175" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="X175" t="n">
         <v>6</v>
@@ -81526,7 +81526,7 @@
         <v>6</v>
       </c>
       <c r="CV175" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="CW175" t="n">
         <v>1</v>
@@ -83948,6 +83948,462 @@
       <c r="EL180" t="inlineStr">
         <is>
           <t>2.10</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Turkey_Süper_Lig_2025-2026</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>2025/2026</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>20</v>
+      </c>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>Kocaelispor</t>
+        </is>
+      </c>
+      <c r="E181" t="inlineStr">
+        <is>
+          <t>Fenerbahçe</t>
+        </is>
+      </c>
+      <c r="F181" s="2" t="n">
+        <v>46055.70833333334</v>
+      </c>
+      <c r="G181" t="n">
+        <v>0</v>
+      </c>
+      <c r="H181" t="n">
+        <v>2</v>
+      </c>
+      <c r="I181" t="n">
+        <v>2</v>
+      </c>
+      <c r="J181" t="n">
+        <v>8</v>
+      </c>
+      <c r="K181" t="n">
+        <v>3</v>
+      </c>
+      <c r="L181" t="n">
+        <v>11</v>
+      </c>
+      <c r="M181" t="n">
+        <v>2</v>
+      </c>
+      <c r="N181" t="n">
+        <v>3</v>
+      </c>
+      <c r="O181" t="n">
+        <v>0</v>
+      </c>
+      <c r="P181" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q181" t="n">
+        <v>1</v>
+      </c>
+      <c r="R181" t="n">
+        <v>5</v>
+      </c>
+      <c r="S181" t="n">
+        <v>11</v>
+      </c>
+      <c r="T181" t="n">
+        <v>4</v>
+      </c>
+      <c r="U181" t="n">
+        <v>12</v>
+      </c>
+      <c r="V181" t="n">
+        <v>9</v>
+      </c>
+      <c r="W181" t="n">
+        <v>17</v>
+      </c>
+      <c r="X181" t="n">
+        <v>14</v>
+      </c>
+      <c r="Y181" t="n">
+        <v>59</v>
+      </c>
+      <c r="Z181" t="n">
+        <v>41</v>
+      </c>
+      <c r="AA181" t="inlineStr">
+        <is>
+          <t>İsmetpaşa Stadyumu</t>
+        </is>
+      </c>
+      <c r="AB181" t="inlineStr">
+        <is>
+          <t>Ankara Caddesi, Kocaeli, İzmit</t>
+        </is>
+      </c>
+      <c r="AC181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AD181" t="n">
+        <v>3</v>
+      </c>
+      <c r="AE181" t="n">
+        <v>5.25</v>
+      </c>
+      <c r="AF181" t="n">
+        <v>3.75</v>
+      </c>
+      <c r="AG181" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AH181" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="AI181" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AJ181" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="AK181" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AL181" t="n">
+        <v>1.91</v>
+      </c>
+      <c r="AM181" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="AN181" t="n">
+        <v>2.46</v>
+      </c>
+      <c r="AO181" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="AP181" t="n">
+        <v>1.66</v>
+      </c>
+      <c r="AQ181" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="AR181" t="n">
+        <v>2.6</v>
+      </c>
+      <c r="AS181" t="n">
+        <v>2.77</v>
+      </c>
+      <c r="AT181" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AU181" t="n">
+        <v>2</v>
+      </c>
+      <c r="AV181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AW181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AX181" t="n">
+        <v>0</v>
+      </c>
+      <c r="AY181" t="n">
+        <v>1</v>
+      </c>
+      <c r="AZ181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BA181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BB181" t="n">
+        <v>105</v>
+      </c>
+      <c r="BC181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BD181" t="n">
+        <v>50</v>
+      </c>
+      <c r="BE181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BF181" t="n">
+        <v>-1</v>
+      </c>
+      <c r="BG181" t="n">
+        <v>2</v>
+      </c>
+      <c r="BH181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BI181" t="n">
+        <v>3</v>
+      </c>
+      <c r="BJ181" t="n">
+        <v>2</v>
+      </c>
+      <c r="BK181" t="n">
+        <v>5</v>
+      </c>
+      <c r="BL181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BM181" t="n">
+        <v>5</v>
+      </c>
+      <c r="BN181" t="n">
+        <v>6</v>
+      </c>
+      <c r="BO181" t="n">
+        <v>2</v>
+      </c>
+      <c r="BP181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BQ181" t="n">
+        <v>0</v>
+      </c>
+      <c r="BR181" t="n">
+        <v>2</v>
+      </c>
+      <c r="BS181" t="n">
+        <v>3</v>
+      </c>
+      <c r="BT181" t="n">
+        <v>2</v>
+      </c>
+      <c r="BU181" t="n">
+        <v>1</v>
+      </c>
+      <c r="BV181" t="n">
+        <v>54</v>
+      </c>
+      <c r="BW181" t="n">
+        <v>24</v>
+      </c>
+      <c r="BX181" t="n">
+        <v>110</v>
+      </c>
+      <c r="BY181" t="n">
+        <v>76</v>
+      </c>
+      <c r="BZ181" t="n">
+        <v>1.23</v>
+      </c>
+      <c r="CA181" t="n">
+        <v>1.1</v>
+      </c>
+      <c r="CB181" t="n">
+        <v>2.32</v>
+      </c>
+      <c r="CC181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CD181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CE181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CF181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CG181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CH181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CI181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CJ181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CK181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CL181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CM181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CN181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CO181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CP181" t="n">
+        <v>0</v>
+      </c>
+      <c r="CQ181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CR181" t="n">
+        <v>31</v>
+      </c>
+      <c r="CS181" t="n">
+        <v>20</v>
+      </c>
+      <c r="CT181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CU181" t="n">
+        <v>14</v>
+      </c>
+      <c r="CV181" t="n">
+        <v>17</v>
+      </c>
+      <c r="CW181" t="n">
+        <v>1</v>
+      </c>
+      <c r="CX181" t="n">
+        <v>3</v>
+      </c>
+      <c r="CY181" t="n">
+        <v>12</v>
+      </c>
+      <c r="CZ181" t="n">
+        <v>40</v>
+      </c>
+      <c r="DA181" t="n">
+        <v>65</v>
+      </c>
+      <c r="DB181" t="n">
+        <v>45</v>
+      </c>
+      <c r="DC181" t="n">
+        <v>60</v>
+      </c>
+      <c r="DD181" t="n">
+        <v>1.64</v>
+      </c>
+      <c r="DE181" t="n">
+        <v>2.27</v>
+      </c>
+      <c r="DF181" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="DG181" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="DH181" t="n">
+        <v>1.26</v>
+      </c>
+      <c r="DI181" t="n">
+        <v>2.26</v>
+      </c>
+      <c r="DJ181" t="n">
+        <v>60</v>
+      </c>
+      <c r="DK181" t="n">
+        <v>35</v>
+      </c>
+      <c r="DL181" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="DM181" t="n">
+        <v>1.7</v>
+      </c>
+      <c r="DN181" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="DO181" t="n">
+        <v>20</v>
+      </c>
+      <c r="DP181" t="b">
+        <v>1</v>
+      </c>
+      <c r="DQ181" t="b">
+        <v>1</v>
+      </c>
+      <c r="DR181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DS181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DT181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DU181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DV181" t="b">
+        <v>0</v>
+      </c>
+      <c r="DW181" t="inlineStr">
+        <is>
+          <t>1.98</t>
+        </is>
+      </c>
+      <c r="DX181" t="inlineStr">
+        <is>
+          <t>3.47</t>
+        </is>
+      </c>
+      <c r="DY181" t="inlineStr">
+        <is>
+          <t>1.31</t>
+        </is>
+      </c>
+      <c r="DZ181" t="inlineStr"/>
+      <c r="EA181" t="inlineStr"/>
+      <c r="EB181" t="inlineStr"/>
+      <c r="EC181" t="inlineStr"/>
+      <c r="ED181" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EE181" t="inlineStr">
+        <is>
+          <t>1.69</t>
+        </is>
+      </c>
+      <c r="EF181" t="inlineStr">
+        <is>
+          <t>2.12</t>
+        </is>
+      </c>
+      <c r="EG181" t="inlineStr">
+        <is>
+          <t>2.13</t>
+        </is>
+      </c>
+      <c r="EH181" t="inlineStr">
+        <is>
+          <t>1.72</t>
+        </is>
+      </c>
+      <c r="EI181" t="inlineStr">
+        <is>
+          <t>5.36</t>
+        </is>
+      </c>
+      <c r="EJ181" t="inlineStr">
+        <is>
+          <t>3.71</t>
+        </is>
+      </c>
+      <c r="EK181" t="inlineStr">
+        <is>
+          <t>1.86</t>
+        </is>
+      </c>
+      <c r="EL181" t="inlineStr">
+        <is>
+          <t>1.99</t>
         </is>
       </c>
     </row>

--- a/data/matches/leagues/Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/matches/leagues/Turkey_Süper_Lig_2025-2026.xlsx
@@ -90841,13 +90841,13 @@
         <v>1</v>
       </c>
       <c r="Q196" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="R196" t="n">
         <v>3</v>
       </c>
       <c r="S196" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="T196" t="n">
         <v>4</v>
@@ -91028,13 +91028,13 @@
         <v>53</v>
       </c>
       <c r="BZ196" t="n">
-        <v>1.74</v>
+        <v>1.67</v>
       </c>
       <c r="CA196" t="n">
         <v>0.79</v>
       </c>
       <c r="CB196" t="n">
-        <v>2.52</v>
+        <v>2.45</v>
       </c>
       <c r="CC196" t="n">
         <v>0</v>

--- a/data/matches/leagues/Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/matches/leagues/Turkey_Süper_Lig_2025-2026.xlsx
@@ -100559,10 +100559,10 @@
         <v>3</v>
       </c>
       <c r="K217" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="L217" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="M217" t="n">
         <v>0</v>
@@ -100577,10 +100577,10 @@
         <v>0</v>
       </c>
       <c r="Q217" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="R217" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="S217" t="n">
         <v>6</v>
@@ -100589,10 +100589,10 @@
         <v>9</v>
       </c>
       <c r="U217" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="V217" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="W217" t="n">
         <v>9</v>
@@ -100764,10 +100764,10 @@
         <v>94</v>
       </c>
       <c r="BZ217" t="n">
-        <v>1.16</v>
+        <v>1.03</v>
       </c>
       <c r="CA217" t="n">
-        <v>1.65</v>
+        <v>1.78</v>
       </c>
       <c r="CB217" t="n">
         <v>2.81</v>

--- a/data/matches/leagues/Turkey_Süper_Lig_2025-2026.xlsx
+++ b/data/matches/leagues/Turkey_Süper_Lig_2025-2026.xlsx
@@ -101775,7 +101775,7 @@
         <v>6</v>
       </c>
       <c r="CY219" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="CZ219" t="n">
         <v>65</v>
@@ -102449,10 +102449,10 @@
         <v>16</v>
       </c>
       <c r="Y221" t="n">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="Z221" t="n">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AA221" t="inlineStr">
         <is>
@@ -102921,10 +102921,10 @@
         <v>19</v>
       </c>
       <c r="Y222" t="n">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="Z222" t="n">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AA222" t="inlineStr">
         <is>
@@ -104773,7 +104773,7 @@
         <v>14</v>
       </c>
       <c r="M226" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="N226" t="n">
         <v>0</v>
@@ -104825,7 +104825,7 @@
         </is>
       </c>
       <c r="AC226" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AD226" t="n">
         <v>0</v>
@@ -104945,7 +104945,7 @@
         <v>0</v>
       </c>
       <c r="BQ226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BR226" t="n">
         <v>0</v>
@@ -104954,7 +104954,7 @@
         <v>3</v>
       </c>
       <c r="BT226" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="BU226" t="n">
         <v>1</v>
